--- a/src/app/store/Vocabulary.xlsx
+++ b/src/app/store/Vocabulary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/projects/fluentor/src/app/store/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB000D2-C32B-224B-9668-87AFB966F4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B473E3-E73C-1548-A815-5EB8FCF47106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12941" uniqueCount="8423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12947" uniqueCount="8429">
   <si>
     <t>id</t>
   </si>
@@ -25304,6 +25304,24 @@
   </si>
   <si>
     <t>yell</t>
+  </si>
+  <si>
+    <t>100 Most Commonly Spoken English Words</t>
+  </si>
+  <si>
+    <t>300 Most Commonly Spoken English Words</t>
+  </si>
+  <si>
+    <t>500 Most Commonly Spoken English Words</t>
+  </si>
+  <si>
+    <t>1000 Most Commonly Spoken English Words</t>
+  </si>
+  <si>
+    <t>the, be, to, of, and, a, in, that, have, i, it, for, not, on, with, he, as, you, do, at, this, but, his, by, from, they, we, say, her, she, or, an, will, my, one, all, would, there, their, what, so, up, out, if, about, who, get, which, go, me, when, make, can, like, time, no, just, him, know, take, people, into, year, your, good, some, could, them, see, other, than, then, now, look, only, come, its, over, think, also, back, after, use, two, how, our, work, first, well, way, even, new, want, because, any, these, give, day, most, us</t>
+  </si>
+  <si>
+    <t>the, be, to, of, and, a, in, that, have, I, it, for, not, on, with, he, as, you, do, at, this, but, his, by, from, they, we, say, her, she, or, an, will, my, one, all, would, there, their, what, so, up, out, if, about, who, get, which, go, me, when, make, can, like, time, no, just, him, know, take, person, into, year, your, good, some, could, them, see, other, than, then, now, look, only, come, its, over, think, also, back, after, use, two, how, our, work, first, well, way, even, new, want, because, any, each, give, day, most, us, is, are, was, were, been, did, does, doing, had, having, may, might, must, should, shall, here, where, why, again, still, always, never, often, sometimes, very, really, much, many, more, less, few, lot, something, anything, everything, nothing, someone, anyone, everyone, thing, place, man, woman, child, friend, family, job, life, world, today, tomorrow, yesterday, morning, night, moment, point, fact, idea, problem, question, answer, reason, part, end, side, group, number, company, system, program, service, information, money, level, order, change, result, issue, process, story, name, area, line, power, room, home, school, state, country, city, hand, eye, head, face, voice, word, kind, type, law, government, business, market, team, member, leader, manager, worker, customer, user, body, mind, heart, health, care, help, support, control, grow, build, create, start, stop, begin, finish, open, close, move, stay, leave, return, bring, send, call, talk, speak, tell, ask, listen, hear, watch, find, lose, keep, hold, put, set, let, try, need, feel, believe, understand, remember, forget, learn, teach, study, play, run, walk, sit, stand, live, die, eat, drink, sleep, wake, buy, sell, pay, cost, drive, ride, travel, meet, join, share, follow, lead, win, break, fix, improve, develop, plan, decide, choose, agree, accept, refuse, offer, request, allow, prevent, protect, save, risk, succeed, continue</t>
   </si>
 </sst>
 </file>
@@ -25459,7 +25477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -25492,6 +25510,9 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -28911,7 +28932,7 @@
         <v>2363</v>
       </c>
       <c r="F137" s="4" t="str">
-        <f t="shared" ref="F137:F152" si="3">_xlfn.CONCAT(A137,".mp3")</f>
+        <f t="shared" ref="F137:F156" si="3">_xlfn.CONCAT(A137,".mp3")</f>
         <v>136.mp3</v>
       </c>
       <c r="H137" s="6" t="s">
@@ -29219,6 +29240,9 @@
       <c r="B152" s="1">
         <v>12</v>
       </c>
+      <c r="C152" s="4" t="s">
+        <v>8423</v>
+      </c>
       <c r="F152" s="4" t="str">
         <f t="shared" si="3"/>
         <v>151.mp3</v>
@@ -29227,10 +29251,63 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="14.25" customHeight="1"/>
-    <row r="154" spans="1:8" ht="14.25" customHeight="1"/>
-    <row r="155" spans="1:8" ht="14.25" customHeight="1"/>
-    <row r="156" spans="1:8" ht="14.25" customHeight="1"/>
+    <row r="153" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A153" s="1">
+        <v>152</v>
+      </c>
+      <c r="B153" s="1">
+        <v>12</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>8424</v>
+      </c>
+      <c r="F153" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>152.mp3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A154" s="1">
+        <v>153</v>
+      </c>
+      <c r="B154" s="1">
+        <v>12</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>8425</v>
+      </c>
+      <c r="F154" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>153.mp3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A155" s="1">
+        <v>154</v>
+      </c>
+      <c r="B155" s="1">
+        <v>12</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>8426</v>
+      </c>
+      <c r="F155" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>154.mp3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="14.25" customHeight="1">
+      <c r="A156" s="1">
+        <v>155</v>
+      </c>
+      <c r="B156" s="1">
+        <v>12</v>
+      </c>
+      <c r="F156" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v>155.mp3</v>
+      </c>
+    </row>
     <row r="157" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="158" spans="1:8" ht="14.25" customHeight="1"/>
     <row r="159" spans="1:8" ht="14.25" customHeight="1"/>
@@ -29972,11 +30049,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4190A7-BF61-6C4B-9083-2F021021C2BE}">
-  <dimension ref="A1:M2767"/>
+  <dimension ref="A1:M2917"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.5" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="57.6640625" customWidth="1"/>
     <col min="4" max="9" width="16.83203125" customWidth="1"/>
     <col min="10" max="10" width="27.1640625" customWidth="1"/>
     <col min="11" max="11" width="21.33203125" customWidth="1"/>
@@ -91686,10 +91763,473 @@
         <v>8422</v>
       </c>
     </row>
-    <row r="2767" spans="2:3">
+    <row r="2767" spans="2:3" ht="112">
       <c r="B2767" s="4">
         <v>151</v>
       </c>
+      <c r="C2767" s="22" t="s">
+        <v>8427</v>
+      </c>
+    </row>
+    <row r="2768" spans="2:3" ht="409.6">
+      <c r="B2768" s="4">
+        <v>152</v>
+      </c>
+      <c r="C2768" s="22" t="s">
+        <v>8428</v>
+      </c>
+    </row>
+    <row r="2769" spans="2:3">
+      <c r="B2769" s="4">
+        <v>153</v>
+      </c>
+      <c r="C2769" s="22"/>
+    </row>
+    <row r="2770" spans="2:3">
+      <c r="B2770" s="4">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2771" spans="2:3">
+      <c r="B2771" s="4"/>
+    </row>
+    <row r="2772" spans="2:3">
+      <c r="B2772" s="4"/>
+    </row>
+    <row r="2773" spans="2:3">
+      <c r="B2773" s="4"/>
+    </row>
+    <row r="2774" spans="2:3">
+      <c r="B2774" s="4"/>
+    </row>
+    <row r="2775" spans="2:3">
+      <c r="B2775" s="4"/>
+    </row>
+    <row r="2776" spans="2:3">
+      <c r="B2776" s="4"/>
+    </row>
+    <row r="2777" spans="2:3">
+      <c r="B2777" s="4"/>
+    </row>
+    <row r="2778" spans="2:3">
+      <c r="B2778" s="4"/>
+    </row>
+    <row r="2779" spans="2:3">
+      <c r="B2779" s="4"/>
+    </row>
+    <row r="2780" spans="2:3">
+      <c r="B2780" s="4"/>
+    </row>
+    <row r="2781" spans="2:3">
+      <c r="B2781" s="4"/>
+    </row>
+    <row r="2782" spans="2:3">
+      <c r="B2782" s="4"/>
+    </row>
+    <row r="2783" spans="2:3">
+      <c r="B2783" s="4"/>
+    </row>
+    <row r="2784" spans="2:3">
+      <c r="B2784" s="4"/>
+    </row>
+    <row r="2785" spans="2:2">
+      <c r="B2785" s="4"/>
+    </row>
+    <row r="2786" spans="2:2">
+      <c r="B2786" s="4"/>
+    </row>
+    <row r="2787" spans="2:2">
+      <c r="B2787" s="4"/>
+    </row>
+    <row r="2788" spans="2:2">
+      <c r="B2788" s="4"/>
+    </row>
+    <row r="2789" spans="2:2">
+      <c r="B2789" s="4"/>
+    </row>
+    <row r="2790" spans="2:2">
+      <c r="B2790" s="4"/>
+    </row>
+    <row r="2791" spans="2:2">
+      <c r="B2791" s="4"/>
+    </row>
+    <row r="2792" spans="2:2">
+      <c r="B2792" s="4"/>
+    </row>
+    <row r="2793" spans="2:2">
+      <c r="B2793" s="4"/>
+    </row>
+    <row r="2794" spans="2:2">
+      <c r="B2794" s="4"/>
+    </row>
+    <row r="2795" spans="2:2">
+      <c r="B2795" s="4"/>
+    </row>
+    <row r="2796" spans="2:2">
+      <c r="B2796" s="4"/>
+    </row>
+    <row r="2797" spans="2:2">
+      <c r="B2797" s="4"/>
+    </row>
+    <row r="2798" spans="2:2">
+      <c r="B2798" s="4"/>
+    </row>
+    <row r="2799" spans="2:2">
+      <c r="B2799" s="4"/>
+    </row>
+    <row r="2800" spans="2:2">
+      <c r="B2800" s="4"/>
+    </row>
+    <row r="2801" spans="2:2">
+      <c r="B2801" s="4"/>
+    </row>
+    <row r="2802" spans="2:2">
+      <c r="B2802" s="4"/>
+    </row>
+    <row r="2803" spans="2:2">
+      <c r="B2803" s="4"/>
+    </row>
+    <row r="2804" spans="2:2">
+      <c r="B2804" s="4"/>
+    </row>
+    <row r="2805" spans="2:2">
+      <c r="B2805" s="4"/>
+    </row>
+    <row r="2806" spans="2:2">
+      <c r="B2806" s="4"/>
+    </row>
+    <row r="2807" spans="2:2">
+      <c r="B2807" s="4"/>
+    </row>
+    <row r="2808" spans="2:2">
+      <c r="B2808" s="4"/>
+    </row>
+    <row r="2809" spans="2:2">
+      <c r="B2809" s="4"/>
+    </row>
+    <row r="2810" spans="2:2">
+      <c r="B2810" s="4"/>
+    </row>
+    <row r="2811" spans="2:2">
+      <c r="B2811" s="4"/>
+    </row>
+    <row r="2812" spans="2:2">
+      <c r="B2812" s="4"/>
+    </row>
+    <row r="2813" spans="2:2">
+      <c r="B2813" s="4"/>
+    </row>
+    <row r="2814" spans="2:2">
+      <c r="B2814" s="4"/>
+    </row>
+    <row r="2815" spans="2:2">
+      <c r="B2815" s="4"/>
+    </row>
+    <row r="2816" spans="2:2">
+      <c r="B2816" s="4"/>
+    </row>
+    <row r="2817" spans="2:2">
+      <c r="B2817" s="4"/>
+    </row>
+    <row r="2818" spans="2:2">
+      <c r="B2818" s="4"/>
+    </row>
+    <row r="2819" spans="2:2">
+      <c r="B2819" s="4"/>
+    </row>
+    <row r="2820" spans="2:2">
+      <c r="B2820" s="4"/>
+    </row>
+    <row r="2821" spans="2:2">
+      <c r="B2821" s="4"/>
+    </row>
+    <row r="2822" spans="2:2">
+      <c r="B2822" s="4"/>
+    </row>
+    <row r="2823" spans="2:2">
+      <c r="B2823" s="4"/>
+    </row>
+    <row r="2824" spans="2:2">
+      <c r="B2824" s="4"/>
+    </row>
+    <row r="2825" spans="2:2">
+      <c r="B2825" s="4"/>
+    </row>
+    <row r="2826" spans="2:2">
+      <c r="B2826" s="4"/>
+    </row>
+    <row r="2827" spans="2:2">
+      <c r="B2827" s="4"/>
+    </row>
+    <row r="2828" spans="2:2">
+      <c r="B2828" s="4"/>
+    </row>
+    <row r="2829" spans="2:2">
+      <c r="B2829" s="4"/>
+    </row>
+    <row r="2830" spans="2:2">
+      <c r="B2830" s="4"/>
+    </row>
+    <row r="2831" spans="2:2">
+      <c r="B2831" s="4"/>
+    </row>
+    <row r="2832" spans="2:2">
+      <c r="B2832" s="4"/>
+    </row>
+    <row r="2833" spans="2:2">
+      <c r="B2833" s="4"/>
+    </row>
+    <row r="2834" spans="2:2">
+      <c r="B2834" s="4"/>
+    </row>
+    <row r="2835" spans="2:2">
+      <c r="B2835" s="4"/>
+    </row>
+    <row r="2836" spans="2:2">
+      <c r="B2836" s="4"/>
+    </row>
+    <row r="2837" spans="2:2">
+      <c r="B2837" s="4"/>
+    </row>
+    <row r="2838" spans="2:2">
+      <c r="B2838" s="4"/>
+    </row>
+    <row r="2839" spans="2:2">
+      <c r="B2839" s="4"/>
+    </row>
+    <row r="2840" spans="2:2">
+      <c r="B2840" s="4"/>
+    </row>
+    <row r="2841" spans="2:2">
+      <c r="B2841" s="4"/>
+    </row>
+    <row r="2842" spans="2:2">
+      <c r="B2842" s="4"/>
+    </row>
+    <row r="2843" spans="2:2">
+      <c r="B2843" s="4"/>
+    </row>
+    <row r="2844" spans="2:2">
+      <c r="B2844" s="4"/>
+    </row>
+    <row r="2845" spans="2:2">
+      <c r="B2845" s="4"/>
+    </row>
+    <row r="2846" spans="2:2">
+      <c r="B2846" s="4"/>
+    </row>
+    <row r="2847" spans="2:2">
+      <c r="B2847" s="4"/>
+    </row>
+    <row r="2848" spans="2:2">
+      <c r="B2848" s="4"/>
+    </row>
+    <row r="2849" spans="2:2">
+      <c r="B2849" s="4"/>
+    </row>
+    <row r="2850" spans="2:2">
+      <c r="B2850" s="4"/>
+    </row>
+    <row r="2851" spans="2:2">
+      <c r="B2851" s="4"/>
+    </row>
+    <row r="2852" spans="2:2">
+      <c r="B2852" s="4"/>
+    </row>
+    <row r="2853" spans="2:2">
+      <c r="B2853" s="4"/>
+    </row>
+    <row r="2854" spans="2:2">
+      <c r="B2854" s="4"/>
+    </row>
+    <row r="2855" spans="2:2">
+      <c r="B2855" s="4"/>
+    </row>
+    <row r="2856" spans="2:2">
+      <c r="B2856" s="4"/>
+    </row>
+    <row r="2857" spans="2:2">
+      <c r="B2857" s="4"/>
+    </row>
+    <row r="2858" spans="2:2">
+      <c r="B2858" s="4"/>
+    </row>
+    <row r="2859" spans="2:2">
+      <c r="B2859" s="4"/>
+    </row>
+    <row r="2860" spans="2:2">
+      <c r="B2860" s="4"/>
+    </row>
+    <row r="2861" spans="2:2">
+      <c r="B2861" s="4"/>
+    </row>
+    <row r="2862" spans="2:2">
+      <c r="B2862" s="4"/>
+    </row>
+    <row r="2863" spans="2:2">
+      <c r="B2863" s="4"/>
+    </row>
+    <row r="2864" spans="2:2">
+      <c r="B2864" s="4"/>
+    </row>
+    <row r="2865" spans="2:2">
+      <c r="B2865" s="4"/>
+    </row>
+    <row r="2866" spans="2:2">
+      <c r="B2866" s="4"/>
+    </row>
+    <row r="2867" spans="2:2">
+      <c r="B2867" s="4"/>
+    </row>
+    <row r="2868" spans="2:2">
+      <c r="B2868" s="4"/>
+    </row>
+    <row r="2869" spans="2:2">
+      <c r="B2869" s="4"/>
+    </row>
+    <row r="2870" spans="2:2">
+      <c r="B2870" s="4"/>
+    </row>
+    <row r="2871" spans="2:2">
+      <c r="B2871" s="4"/>
+    </row>
+    <row r="2872" spans="2:2">
+      <c r="B2872" s="4"/>
+    </row>
+    <row r="2873" spans="2:2">
+      <c r="B2873" s="4"/>
+    </row>
+    <row r="2874" spans="2:2">
+      <c r="B2874" s="4"/>
+    </row>
+    <row r="2875" spans="2:2">
+      <c r="B2875" s="4"/>
+    </row>
+    <row r="2876" spans="2:2">
+      <c r="B2876" s="4"/>
+    </row>
+    <row r="2877" spans="2:2">
+      <c r="B2877" s="4"/>
+    </row>
+    <row r="2878" spans="2:2">
+      <c r="B2878" s="4"/>
+    </row>
+    <row r="2879" spans="2:2">
+      <c r="B2879" s="4"/>
+    </row>
+    <row r="2880" spans="2:2">
+      <c r="B2880" s="4"/>
+    </row>
+    <row r="2881" spans="2:2">
+      <c r="B2881" s="4"/>
+    </row>
+    <row r="2882" spans="2:2">
+      <c r="B2882" s="4"/>
+    </row>
+    <row r="2883" spans="2:2">
+      <c r="B2883" s="4"/>
+    </row>
+    <row r="2884" spans="2:2">
+      <c r="B2884" s="4"/>
+    </row>
+    <row r="2885" spans="2:2">
+      <c r="B2885" s="4"/>
+    </row>
+    <row r="2886" spans="2:2">
+      <c r="B2886" s="4"/>
+    </row>
+    <row r="2887" spans="2:2">
+      <c r="B2887" s="4"/>
+    </row>
+    <row r="2888" spans="2:2">
+      <c r="B2888" s="4"/>
+    </row>
+    <row r="2889" spans="2:2">
+      <c r="B2889" s="4"/>
+    </row>
+    <row r="2890" spans="2:2">
+      <c r="B2890" s="4"/>
+    </row>
+    <row r="2891" spans="2:2">
+      <c r="B2891" s="4"/>
+    </row>
+    <row r="2892" spans="2:2">
+      <c r="B2892" s="4"/>
+    </row>
+    <row r="2893" spans="2:2">
+      <c r="B2893" s="4"/>
+    </row>
+    <row r="2894" spans="2:2">
+      <c r="B2894" s="4"/>
+    </row>
+    <row r="2895" spans="2:2">
+      <c r="B2895" s="4"/>
+    </row>
+    <row r="2896" spans="2:2">
+      <c r="B2896" s="4"/>
+    </row>
+    <row r="2897" spans="2:2">
+      <c r="B2897" s="4"/>
+    </row>
+    <row r="2898" spans="2:2">
+      <c r="B2898" s="4"/>
+    </row>
+    <row r="2899" spans="2:2">
+      <c r="B2899" s="4"/>
+    </row>
+    <row r="2900" spans="2:2">
+      <c r="B2900" s="4"/>
+    </row>
+    <row r="2901" spans="2:2">
+      <c r="B2901" s="4"/>
+    </row>
+    <row r="2902" spans="2:2">
+      <c r="B2902" s="4"/>
+    </row>
+    <row r="2903" spans="2:2">
+      <c r="B2903" s="4"/>
+    </row>
+    <row r="2904" spans="2:2">
+      <c r="B2904" s="4"/>
+    </row>
+    <row r="2905" spans="2:2">
+      <c r="B2905" s="4"/>
+    </row>
+    <row r="2906" spans="2:2">
+      <c r="B2906" s="4"/>
+    </row>
+    <row r="2907" spans="2:2">
+      <c r="B2907" s="4"/>
+    </row>
+    <row r="2908" spans="2:2">
+      <c r="B2908" s="4"/>
+    </row>
+    <row r="2909" spans="2:2">
+      <c r="B2909" s="4"/>
+    </row>
+    <row r="2910" spans="2:2">
+      <c r="B2910" s="4"/>
+    </row>
+    <row r="2911" spans="2:2">
+      <c r="B2911" s="4"/>
+    </row>
+    <row r="2912" spans="2:2">
+      <c r="B2912" s="4"/>
+    </row>
+    <row r="2913" spans="2:2">
+      <c r="B2913" s="4"/>
+    </row>
+    <row r="2914" spans="2:2">
+      <c r="B2914" s="4"/>
+    </row>
+    <row r="2915" spans="2:2">
+      <c r="B2915" s="4"/>
+    </row>
+    <row r="2916" spans="2:2">
+      <c r="B2916" s="4"/>
+    </row>
+    <row r="2917" spans="2:2">
+      <c r="B2917" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
